--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1CCD13C9-D95B-4E3C-9095-F205276EC08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{257C05E1-FD2E-4CC7-9F85-0C6C6A46EF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2E92B48B-46FC-4C99-95E5-D0573F327503}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>UserName</t>
   </si>
@@ -47,38 +47,30 @@
     <t>Laxmi</t>
   </si>
   <si>
+    <t>laksh@yahoo.com</t>
+  </si>
+  <si>
+    <t>laks@yahoo.com</t>
+  </si>
+  <si>
+    <t>abc123@gmail.com</t>
+  </si>
+  <si>
+    <t>Lakshmi</t>
+  </si>
+  <si>
+    <t>xyz</t>
+  </si>
+  <si>
     <t>Invalid</t>
-  </si>
-  <si>
-    <t>laksh@yahoo.com</t>
-  </si>
-  <si>
-    <t>Lakshmi</t>
-  </si>
-  <si>
-    <t>laks@yahoo.com</t>
-  </si>
-  <si>
-    <t>xyz</t>
-  </si>
-  <si>
-    <t>pqrst12345@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -134,17 +126,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -182,7 +177,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -194,7 +189,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -241,6 +236,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -276,6 +288,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -427,90 +456,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46A4715-9E35-40E2-8ACB-08E6E2F33DB3}">
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.26953125" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="1" max="1" width="21.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{E1527645-F076-4AA1-9288-7C7A41872BBD}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{3895A462-36D4-4CFC-BB47-2E8A7E5D3D9B}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{20F77376-835A-4B06-A191-A12609759981}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{320FA94F-2EB1-4C5D-875D-D10C83E75AEA}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{58577580-C7EE-4C76-AFC6-362CBA99E2D3}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{E9C98614-8824-441E-817F-330B497F9FF9}"/>
-    <hyperlink ref="B6" r:id="rId7" xr:uid="{B33373D4-624C-4940-AF3C-B2167195EC72}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{69FAADCD-539F-49C3-AE77-C9366C1B319B}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{1A65CD5C-D74A-4EA7-9296-7AB763F76FF0}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{F44F2013-F14C-41C4-9433-02C4FFCE81F5}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{9EA1B368-AEF4-48F9-A9AF-391D52526DD1}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{1F4A9F41-F12A-441F-AC0D-0FC02DE2B296}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{95516910-2CC8-4028-834C-C376E8EE6261}"/>
+    <hyperlink ref="B6" r:id="rId7" xr:uid="{97ED5FCB-0945-41A4-85FF-307E55B86745}"/>
+    <hyperlink ref="B7" r:id="rId8" xr:uid="{42F4C2C4-B675-4366-9583-E3B739EFEE6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
